--- a/fhir/CodeSystem-urn-oid-1.2.208.184.100.8.xlsx
+++ b/fhir/CodeSystem-urn-oid-1.2.208.184.100.8.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="1132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="1135">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -526,10 +526,10 @@
     <t>MCS88050</t>
   </si>
   <si>
-    <t>Rejse sætte sig testen;Pt</t>
-  </si>
-  <si>
-    <t>Pt—Rejse sætte sig testen; antal (værdi 0-50) =  × 1/30s</t>
+    <t>Rejse sætte sig testen(30 sek.);Pt</t>
+  </si>
+  <si>
+    <t>Pt—Rejse sætte sig testen; antal (værdi 0-50) (målt over 30 sekunder) =  × 1/30s</t>
   </si>
   <si>
     <t>MCS88052</t>
@@ -1619,6 +1619,15 @@
   </si>
   <si>
     <t>Pt—Alcohol Use Disorder Test; antal (værdi 0-12) = ?</t>
+  </si>
+  <si>
+    <t>MCS88214</t>
+  </si>
+  <si>
+    <t>Rejse sætte sig testen(60 sek.);Pt</t>
+  </si>
+  <si>
+    <t>Pt—Rejse sætte sig testen; antal (værdi 0-100) (målt over 60 sekunder) =  × 1/60s</t>
   </si>
   <si>
     <t>MCS89001</t>
@@ -3761,7 +3770,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D433"/>
+  <dimension ref="A1:D434"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -6113,7 +6122,7 @@
         <v>539</v>
       </c>
       <c r="D168" t="s" s="2">
-        <v>526</v>
+        <v>540</v>
       </c>
     </row>
     <row r="169">
@@ -6121,13 +6130,13 @@
         <v>47</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D169" t="s" s="2">
-        <v>541</v>
+        <v>526</v>
       </c>
     </row>
     <row r="170">
@@ -6135,13 +6144,13 @@
         <v>47</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D170" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="171">
@@ -6149,13 +6158,13 @@
         <v>47</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D171" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="172">
@@ -6163,13 +6172,13 @@
         <v>47</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D172" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="173">
@@ -6177,13 +6186,13 @@
         <v>47</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D173" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="174">
@@ -6191,13 +6200,13 @@
         <v>47</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D174" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="175">
@@ -6205,10 +6214,10 @@
         <v>47</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D175" t="s" s="2">
         <v>554</v>
@@ -6239,7 +6248,7 @@
         <v>559</v>
       </c>
       <c r="D177" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="178">
@@ -6247,13 +6256,13 @@
         <v>47</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D178" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="179">
@@ -6261,13 +6270,13 @@
         <v>47</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D179" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="180">
@@ -6275,13 +6284,13 @@
         <v>47</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D180" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="181">
@@ -6289,13 +6298,13 @@
         <v>47</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D181" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="182">
@@ -6303,13 +6312,13 @@
         <v>47</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D182" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="183">
@@ -6317,13 +6326,13 @@
         <v>47</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D183" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="184">
@@ -6331,13 +6340,13 @@
         <v>47</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D184" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="185">
@@ -6345,10 +6354,10 @@
         <v>47</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D185" t="s" s="2">
         <v>576</v>
@@ -6365,7 +6374,7 @@
         <v>578</v>
       </c>
       <c r="D186" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="187">
@@ -6373,13 +6382,13 @@
         <v>47</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D187" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="188">
@@ -6387,13 +6396,13 @@
         <v>47</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D188" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="189">
@@ -6401,10 +6410,10 @@
         <v>47</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D189" t="s" s="2">
         <v>585</v>
@@ -6435,7 +6444,7 @@
         <v>590</v>
       </c>
       <c r="D191" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="192">
@@ -6443,13 +6452,13 @@
         <v>47</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D192" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="193">
@@ -6457,10 +6466,10 @@
         <v>47</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D193" t="s" s="2">
         <v>595</v>
@@ -6519,7 +6528,7 @@
         <v>606</v>
       </c>
       <c r="D197" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="198">
@@ -6527,13 +6536,13 @@
         <v>47</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D198" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="199">
@@ -6541,13 +6550,13 @@
         <v>47</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D199" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="200">
@@ -6555,13 +6564,13 @@
         <v>47</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D200" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="201">
@@ -6569,10 +6578,10 @@
         <v>47</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D201" t="s" s="2">
         <v>615</v>
@@ -6603,7 +6612,7 @@
         <v>620</v>
       </c>
       <c r="D203" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="204">
@@ -6611,13 +6620,13 @@
         <v>47</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D204" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="205">
@@ -6625,13 +6634,13 @@
         <v>47</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D205" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="206">
@@ -6639,13 +6648,13 @@
         <v>47</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D206" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="207">
@@ -6653,13 +6662,13 @@
         <v>47</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D207" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="208">
@@ -6667,13 +6676,13 @@
         <v>47</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D208" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="209">
@@ -6681,10 +6690,10 @@
         <v>47</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D209" t="s" s="2">
         <v>633</v>
@@ -6743,7 +6752,7 @@
         <v>644</v>
       </c>
       <c r="D213" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="214">
@@ -6751,13 +6760,13 @@
         <v>47</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D214" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="215">
@@ -6765,13 +6774,13 @@
         <v>47</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D215" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="216">
@@ -6779,13 +6788,13 @@
         <v>47</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D216" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="217">
@@ -6793,13 +6802,13 @@
         <v>47</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D217" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="218">
@@ -6807,13 +6816,13 @@
         <v>47</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D218" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="219">
@@ -6821,13 +6830,13 @@
         <v>47</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D219" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="220">
@@ -6835,13 +6844,13 @@
         <v>47</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D220" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="221">
@@ -6849,13 +6858,13 @@
         <v>47</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D221" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="222">
@@ -6863,13 +6872,13 @@
         <v>47</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D222" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="223">
@@ -6877,13 +6886,13 @@
         <v>47</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D223" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="224">
@@ -6891,13 +6900,13 @@
         <v>47</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D224" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="225">
@@ -6905,13 +6914,13 @@
         <v>47</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D225" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="226">
@@ -6919,13 +6928,13 @@
         <v>47</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D226" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="227">
@@ -6933,13 +6942,13 @@
         <v>47</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D227" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="228">
@@ -6947,13 +6956,13 @@
         <v>47</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D228" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="229">
@@ -6961,13 +6970,13 @@
         <v>47</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D229" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="230">
@@ -6975,13 +6984,13 @@
         <v>47</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D230" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="231">
@@ -6989,13 +6998,13 @@
         <v>47</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D231" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="232">
@@ -7003,13 +7012,13 @@
         <v>47</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D232" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="233">
@@ -7017,10 +7026,10 @@
         <v>47</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D233" t="s" s="2">
         <v>685</v>
@@ -7051,7 +7060,7 @@
         <v>690</v>
       </c>
       <c r="D235" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="236">
@@ -7059,13 +7068,13 @@
         <v>47</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D236" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="237">
@@ -7073,13 +7082,13 @@
         <v>47</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D237" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="238">
@@ -7087,13 +7096,13 @@
         <v>47</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D238" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="239">
@@ -7101,13 +7110,13 @@
         <v>47</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D239" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="240">
@@ -7115,13 +7124,13 @@
         <v>47</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D240" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="241">
@@ -7129,13 +7138,13 @@
         <v>47</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D241" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="242">
@@ -7143,13 +7152,13 @@
         <v>47</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D242" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="243">
@@ -7157,13 +7166,13 @@
         <v>47</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C243" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D243" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="244">
@@ -7171,13 +7180,13 @@
         <v>47</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C244" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D244" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="245">
@@ -7185,10 +7194,10 @@
         <v>47</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C245" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D245" t="s" s="2">
         <v>711</v>
@@ -7401,7 +7410,7 @@
         <v>755</v>
       </c>
       <c r="D260" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="261">
@@ -7409,13 +7418,13 @@
         <v>47</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C261" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D261" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="262">
@@ -7423,13 +7432,13 @@
         <v>47</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C262" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D262" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="263">
@@ -7437,13 +7446,13 @@
         <v>47</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C263" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D263" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="264">
@@ -7451,13 +7460,13 @@
         <v>47</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C264" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D264" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="265">
@@ -7465,13 +7474,13 @@
         <v>47</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C265" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D265" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="266">
@@ -7479,13 +7488,13 @@
         <v>47</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C266" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D266" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="267">
@@ -7493,13 +7502,13 @@
         <v>47</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C267" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D267" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="268">
@@ -7507,13 +7516,13 @@
         <v>47</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C268" t="s" s="2">
-        <v>755</v>
+        <v>772</v>
       </c>
       <c r="D268" t="s" s="2">
-        <v>755</v>
+        <v>772</v>
       </c>
     </row>
     <row r="269">
@@ -7521,13 +7530,13 @@
         <v>47</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="C269" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D269" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="270">
@@ -7535,13 +7544,13 @@
         <v>47</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C270" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D270" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="271">
@@ -7549,13 +7558,13 @@
         <v>47</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C271" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D271" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="272">
@@ -7563,13 +7572,13 @@
         <v>47</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C272" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D272" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="273">
@@ -7577,13 +7586,13 @@
         <v>47</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D273" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="274">
@@ -7591,13 +7600,13 @@
         <v>47</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="C274" t="s" s="2">
-        <v>777</v>
+        <v>768</v>
       </c>
       <c r="D274" t="s" s="2">
-        <v>777</v>
+        <v>768</v>
       </c>
     </row>
     <row r="275">
@@ -7605,13 +7614,13 @@
         <v>47</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C275" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D275" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="276">
@@ -7619,13 +7628,13 @@
         <v>47</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C276" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D276" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="277">
@@ -7633,13 +7642,13 @@
         <v>47</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C277" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D277" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="278">
@@ -7647,10 +7656,10 @@
         <v>47</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C278" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D278" t="s" s="2">
         <v>786</v>
@@ -7765,7 +7774,7 @@
         <v>809</v>
       </c>
       <c r="D286" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="287">
@@ -7773,13 +7782,13 @@
         <v>47</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C287" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D287" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="288">
@@ -7787,13 +7796,13 @@
         <v>47</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C288" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D288" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="289">
@@ -7801,13 +7810,13 @@
         <v>47</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C289" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D289" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="290">
@@ -7815,13 +7824,13 @@
         <v>47</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C290" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D290" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="291">
@@ -7829,13 +7838,13 @@
         <v>47</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D291" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="292">
@@ -7843,13 +7852,13 @@
         <v>47</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D292" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="293">
@@ -7857,13 +7866,13 @@
         <v>47</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C293" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D293" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="294">
@@ -7871,13 +7880,13 @@
         <v>47</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C294" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D294" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="295">
@@ -7885,13 +7894,13 @@
         <v>47</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C295" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D295" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="296">
@@ -7899,13 +7908,13 @@
         <v>47</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C296" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D296" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="297">
@@ -7913,13 +7922,13 @@
         <v>47</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C297" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D297" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="298">
@@ -7927,13 +7936,13 @@
         <v>47</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C298" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D298" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="299">
@@ -7941,13 +7950,13 @@
         <v>47</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C299" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D299" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="300">
@@ -7955,13 +7964,13 @@
         <v>47</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C300" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D300" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="301">
@@ -7969,13 +7978,13 @@
         <v>47</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C301" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D301" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="302">
@@ -7983,13 +7992,13 @@
         <v>47</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C302" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D302" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="303">
@@ -7997,13 +8006,13 @@
         <v>47</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C303" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D303" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="304">
@@ -8011,13 +8020,13 @@
         <v>47</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C304" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D304" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="305">
@@ -8025,13 +8034,13 @@
         <v>47</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D305" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="306">
@@ -8039,13 +8048,13 @@
         <v>47</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C306" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D306" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="307">
@@ -8053,13 +8062,13 @@
         <v>47</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C307" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D307" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="308">
@@ -8067,13 +8076,13 @@
         <v>47</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C308" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D308" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="309">
@@ -8081,13 +8090,13 @@
         <v>47</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C309" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D309" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="310">
@@ -8095,13 +8104,13 @@
         <v>47</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D310" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="311">
@@ -8109,13 +8118,13 @@
         <v>47</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D311" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="312">
@@ -8123,13 +8132,13 @@
         <v>47</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="D312" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="313">
@@ -8137,13 +8146,13 @@
         <v>47</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D313" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="314">
@@ -8151,13 +8160,13 @@
         <v>47</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D314" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="315">
@@ -8165,13 +8174,13 @@
         <v>47</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="D315" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="316">
@@ -8179,13 +8188,13 @@
         <v>47</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D316" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="317">
@@ -8193,13 +8202,13 @@
         <v>47</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="D317" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="318">
@@ -8207,13 +8216,13 @@
         <v>47</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C318" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D318" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="319">
@@ -8221,13 +8230,13 @@
         <v>47</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D319" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="320">
@@ -8235,13 +8244,13 @@
         <v>47</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="D320" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="321">
@@ -8249,13 +8258,13 @@
         <v>47</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>867</v>
+        <v>880</v>
       </c>
       <c r="D321" t="s" s="2">
-        <v>867</v>
+        <v>880</v>
       </c>
     </row>
     <row r="322">
@@ -8263,13 +8272,13 @@
         <v>47</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D322" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="323">
@@ -8277,13 +8286,13 @@
         <v>47</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="D323" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="324">
@@ -8291,13 +8300,13 @@
         <v>47</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D324" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="325">
@@ -8305,13 +8314,13 @@
         <v>47</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D325" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="326">
@@ -8319,13 +8328,13 @@
         <v>47</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="D326" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="327">
@@ -8333,13 +8342,13 @@
         <v>47</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="C327" t="s" s="2">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="D327" t="s" s="2">
-        <v>885</v>
+        <v>880</v>
       </c>
     </row>
     <row r="328">
@@ -8347,13 +8356,13 @@
         <v>47</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D328" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
     </row>
     <row r="329">
@@ -8361,13 +8370,13 @@
         <v>47</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D329" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="330">
@@ -8375,13 +8384,13 @@
         <v>47</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D330" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
     </row>
     <row r="331">
@@ -8389,13 +8398,13 @@
         <v>47</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D331" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="332">
@@ -8403,13 +8412,13 @@
         <v>47</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D332" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
     </row>
     <row r="333">
@@ -8417,13 +8426,13 @@
         <v>47</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C333" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="D333" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
     </row>
     <row r="334">
@@ -8431,13 +8440,13 @@
         <v>47</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="D334" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
     </row>
     <row r="335">
@@ -8445,13 +8454,13 @@
         <v>47</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C335" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D335" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="336">
@@ -8459,13 +8468,13 @@
         <v>47</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D336" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="337">
@@ -8473,13 +8482,13 @@
         <v>47</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D337" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="338">
@@ -8487,13 +8496,13 @@
         <v>47</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C338" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="D338" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="339">
@@ -8501,13 +8510,13 @@
         <v>47</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C339" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D339" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="340">
@@ -8515,13 +8524,13 @@
         <v>47</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="D340" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="341">
@@ -8529,10 +8538,10 @@
         <v>47</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D341" t="s" s="2">
         <v>914</v>
@@ -8619,7 +8628,7 @@
         <v>931</v>
       </c>
       <c r="D347" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="348">
@@ -8627,13 +8636,13 @@
         <v>47</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C348" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D348" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="349">
@@ -8641,13 +8650,13 @@
         <v>47</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="C349" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="D349" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
     </row>
     <row r="350">
@@ -8655,13 +8664,13 @@
         <v>47</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="D350" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="351">
@@ -8669,13 +8678,13 @@
         <v>47</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D351" t="s" s="2">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="352">
@@ -8683,13 +8692,13 @@
         <v>47</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="D352" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="353">
@@ -8697,10 +8706,10 @@
         <v>47</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="D353" t="s" s="2">
         <v>944</v>
@@ -8728,10 +8737,10 @@
         <v>948</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>767</v>
+        <v>949</v>
       </c>
       <c r="D355" t="s" s="2">
-        <v>767</v>
+        <v>950</v>
       </c>
     </row>
     <row r="356">
@@ -8739,13 +8748,13 @@
         <v>47</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D356" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="357">
@@ -8753,13 +8762,13 @@
         <v>47</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>951</v>
+        <v>772</v>
       </c>
       <c r="D357" t="s" s="2">
-        <v>951</v>
+        <v>772</v>
       </c>
     </row>
     <row r="358">
@@ -8767,13 +8776,13 @@
         <v>47</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="D358" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="359">
@@ -8781,13 +8790,13 @@
         <v>47</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="D359" t="s" s="2">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="360">
@@ -8795,13 +8804,13 @@
         <v>47</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="D360" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="361">
@@ -8809,13 +8818,13 @@
         <v>47</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="D361" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="362">
@@ -8823,13 +8832,13 @@
         <v>47</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="D362" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="363">
@@ -8837,13 +8846,13 @@
         <v>47</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="D363" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="364">
@@ -8851,13 +8860,13 @@
         <v>47</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D364" t="s" s="2">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="365">
@@ -8865,13 +8874,13 @@
         <v>47</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="D365" t="s" s="2">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="366">
@@ -8879,13 +8888,13 @@
         <v>47</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="D366" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="367">
@@ -8893,13 +8902,13 @@
         <v>47</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>763</v>
+        <v>972</v>
       </c>
       <c r="D367" t="s" s="2">
-        <v>763</v>
+        <v>972</v>
       </c>
     </row>
     <row r="368">
@@ -8907,13 +8916,13 @@
         <v>47</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D368" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="369">
@@ -8921,13 +8930,13 @@
         <v>47</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>973</v>
+        <v>768</v>
       </c>
       <c r="D369" t="s" s="2">
-        <v>974</v>
+        <v>768</v>
       </c>
     </row>
     <row r="370">
@@ -9123,7 +9132,7 @@
         <v>1015</v>
       </c>
       <c r="D383" t="s" s="2">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="384">
@@ -9131,13 +9140,13 @@
         <v>47</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="D384" t="s" s="2">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="385">
@@ -9145,13 +9154,13 @@
         <v>47</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="C385" t="s" s="2">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="D385" t="s" s="2">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="386">
@@ -9159,13 +9168,13 @@
         <v>47</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="D386" t="s" s="2">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="387">
@@ -9173,13 +9182,13 @@
         <v>47</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="D387" t="s" s="2">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="388">
@@ -9187,13 +9196,13 @@
         <v>47</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="D388" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="389">
@@ -9201,13 +9210,13 @@
         <v>47</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="C389" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D389" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="390">
@@ -9215,13 +9224,13 @@
         <v>47</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C390" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D390" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="391">
@@ -9229,13 +9238,13 @@
         <v>47</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>763</v>
+        <v>1032</v>
       </c>
       <c r="D391" t="s" s="2">
-        <v>763</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="392">
@@ -9243,13 +9252,13 @@
         <v>47</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="C392" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D392" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="393">
@@ -9257,13 +9266,13 @@
         <v>47</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="C393" t="s" s="2">
-        <v>1033</v>
+        <v>768</v>
       </c>
       <c r="D393" t="s" s="2">
-        <v>1033</v>
+        <v>768</v>
       </c>
     </row>
     <row r="394">
@@ -9271,13 +9280,13 @@
         <v>47</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C394" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="D394" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="395">
@@ -9285,13 +9294,13 @@
         <v>47</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="C395" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D395" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="396">
@@ -9299,13 +9308,13 @@
         <v>47</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="C396" t="s" s="2">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="D396" t="s" s="2">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="397">
@@ -9313,13 +9322,13 @@
         <v>47</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="C397" t="s" s="2">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="D397" t="s" s="2">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="398">
@@ -9327,13 +9336,13 @@
         <v>47</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C398" t="s" s="2">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="D398" t="s" s="2">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="399">
@@ -9341,13 +9350,13 @@
         <v>47</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="C399" t="s" s="2">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="D399" t="s" s="2">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="400">
@@ -9355,13 +9364,13 @@
         <v>47</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="C400" t="s" s="2">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="D400" t="s" s="2">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="401">
@@ -9369,13 +9378,13 @@
         <v>47</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="D401" t="s" s="2">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="402">
@@ -9383,13 +9392,13 @@
         <v>47</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="C402" t="s" s="2">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="D402" t="s" s="2">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="403">
@@ -9397,13 +9406,13 @@
         <v>47</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="C403" t="s" s="2">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="D403" t="s" s="2">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="404">
@@ -9411,13 +9420,13 @@
         <v>47</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="D404" t="s" s="2">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="405">
@@ -9425,10 +9434,10 @@
         <v>47</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="D405" t="s" s="2">
         <v>1058</v>
@@ -9459,7 +9468,7 @@
         <v>1063</v>
       </c>
       <c r="D407" t="s" s="2">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="408">
@@ -9467,13 +9476,13 @@
         <v>47</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="D408" t="s" s="2">
-        <v>1065</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="409">
@@ -9481,10 +9490,10 @@
         <v>47</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="C409" t="s" s="2">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="D409" t="s" s="2">
         <v>1068</v>
@@ -9501,7 +9510,7 @@
         <v>1070</v>
       </c>
       <c r="D410" t="s" s="2">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="411">
@@ -9509,10 +9518,10 @@
         <v>47</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="C411" t="s" s="2">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="D411" t="s" s="2">
         <v>1073</v>
@@ -9599,7 +9608,7 @@
         <v>1090</v>
       </c>
       <c r="D417" t="s" s="2">
-        <v>1090</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="418">
@@ -9607,13 +9616,13 @@
         <v>47</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="D418" t="s" s="2">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="419">
@@ -9621,13 +9630,13 @@
         <v>47</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="D419" t="s" s="2">
-        <v>1094</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="420">
@@ -9635,13 +9644,13 @@
         <v>47</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="D420" t="s" s="2">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="421">
@@ -9649,10 +9658,10 @@
         <v>47</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="D421" t="s" s="2">
         <v>1099</v>
@@ -9725,7 +9734,7 @@
         <v>1113</v>
       </c>
       <c r="D426" t="s" s="2">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="427">
@@ -9733,13 +9742,13 @@
         <v>47</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="C427" t="s" s="2">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D427" t="s" s="2">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="428">
@@ -9747,13 +9756,13 @@
         <v>47</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="C428" t="s" s="2">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="D428" t="s" s="2">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="429">
@@ -9761,10 +9770,10 @@
         <v>47</v>
       </c>
       <c r="B429" t="s" s="2">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="C429" t="s" s="2">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="D429" t="s" s="2">
         <v>1120</v>
@@ -9823,7 +9832,21 @@
         <v>1131</v>
       </c>
       <c r="D433" t="s" s="2">
-        <v>1131</v>
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B434" t="s" s="2">
+        <v>1133</v>
+      </c>
+      <c r="C434" t="s" s="2">
+        <v>1134</v>
+      </c>
+      <c r="D434" t="s" s="2">
+        <v>1134</v>
       </c>
     </row>
   </sheetData>

--- a/fhir/CodeSystem-urn-oid-1.2.208.184.100.8.xlsx
+++ b/fhir/CodeSystem-urn-oid-1.2.208.184.100.8.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-urn-oid-1.2.208.184.100.8.xlsx
+++ b/fhir/CodeSystem-urn-oid-1.2.208.184.100.8.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-urn-oid-1.2.208.184.100.8.xlsx
+++ b/fhir/CodeSystem-urn-oid-1.2.208.184.100.8.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-urn-oid-1.2.208.184.100.8.xlsx
+++ b/fhir/CodeSystem-urn-oid-1.2.208.184.100.8.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-urn-oid-1.2.208.184.100.8.xlsx
+++ b/fhir/CodeSystem-urn-oid-1.2.208.184.100.8.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-urn-oid-1.2.208.184.100.8.xlsx
+++ b/fhir/CodeSystem-urn-oid-1.2.208.184.100.8.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
